--- a/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/01_MC1 - Talep, Etki ve Müşteri Onayı/EKG-PRJ-FRM-26_degisiklik_sonrasi_dogrulama_ve_yeniden_yeterlilik_kayd.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/10_Değişiklik ve Geçici Proses Kontrolü/01_MC1 - Talep, Etki ve Müşteri Onayı/EKG-PRJ-FRM-26_degisiklik_sonrasi_dogrulama_ve_yeniden_yeterlilik_kayd.xlsx
@@ -962,7 +962,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-26&amp;C&amp;"Arial,Regular"&amp;11Değişiklik Sonrası Doğrulama ve Yeniden Yeterlilik Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: İlgisiz ve koşulsuz testler çıkarıldı; değişikliğin gerçek etkisine göre test, kaynak, kanıt ve geçiş kararı tanımlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>